--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783EEC92-01BD-4FEF-9FD0-F50510CA315D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180EC803-9EE8-43CA-BFAF-721D1FE188D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{D762FC6C-BEA3-4FAE-82C9-39772DBD78A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D762FC6C-BEA3-4FAE-82C9-39772DBD78A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1554,6 +1557,7 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:userShapes r:id="rId3"/>
   <c:extLst/>
 </c:chartSpace>
 </file>
@@ -1888,7 +1892,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.4389164843238406E-2"/>
+          <c:y val="9.4056371208247336E-2"/>
+          <c:w val="0.57309610132404853"/>
+          <c:h val="0.90594362879175261"/>
+        </c:manualLayout>
+      </c:layout>
       <c:pieChart>
         <c:varyColors val="1"/>
         <c:ser>
@@ -2295,6 +2309,7 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup orientation="portrait"/>
   </c:printSettings>
+  <c:userShapes r:id="rId3"/>
   <c:extLst/>
 </c:chartSpace>
 </file>
@@ -3345,10 +3360,10 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="107"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="7"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
@@ -3358,12 +3373,10 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
           <a:sp3d contourW="25400">
@@ -3422,12 +3435,10 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
           <a:sp3d contourW="25400">
@@ -3490,12 +3501,10 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
           <a:sp3d contourW="25400">
@@ -3509,12 +3518,10 @@
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
           <a:sp3d contourW="25400">
@@ -3528,12 +3535,10 @@
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
           <a:sp3d contourW="25400">
@@ -3547,12 +3552,10 @@
         <c:idx val="5"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
           <a:sp3d contourW="25400">
@@ -3611,12 +3614,10 @@
         <c:idx val="6"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
           <a:sp3d contourW="25400">
@@ -3679,12 +3680,10 @@
         <c:idx val="7"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
           <a:sp3d contourW="25400">
@@ -3698,12 +3697,10 @@
         <c:idx val="8"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
           <a:sp3d contourW="25400">
@@ -3717,201 +3714,10 @@
         <c:idx val="9"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-          <a:sp3d contourW="25400">
-            <a:contourClr>
-              <a:schemeClr val="lt1"/>
-            </a:contourClr>
-          </a:sp3d>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="10"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-          <a:sp3d contourW="25400">
-            <a:contourClr>
-              <a:schemeClr val="lt1"/>
-            </a:contourClr>
-          </a:sp3d>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="11"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-          <a:sp3d contourW="25400">
-            <a:contourClr>
-              <a:schemeClr val="lt1"/>
-            </a:contourClr>
-          </a:sp3d>
-        </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-60000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout>
-                <c:manualLayout>
-                  <c:w val="0.17287689306216403"/>
-                  <c:h val="0.20534765122676077"/>
-                </c:manualLayout>
-              </c15:layout>
-            </c:ext>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="12"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-          <a:sp3d contourW="25400">
-            <a:contourClr>
-              <a:schemeClr val="lt1"/>
-            </a:contourClr>
-          </a:sp3d>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="13"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-          <a:sp3d contourW="25400">
-            <a:contourClr>
-              <a:schemeClr val="lt1"/>
-            </a:contourClr>
-          </a:sp3d>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="14"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="25400">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
           <a:sp3d contourW="25400">
@@ -3922,335 +3728,232 @@
         </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
-    <c:view3D>
-      <c:rotX val="30"/>
-      <c:rotY val="0"/>
-      <c:depthPercent val="100"/>
-      <c:rAngAx val="0"/>
-    </c:view3D>
-    <c:floor>
-      <c:thickness val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.4881471671555541E-2"/>
+          <c:y val="3.7151702786377708E-2"/>
+          <c:w val="0.94511852832844445"/>
+          <c:h val="0.85883068022069997"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Total</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Crowding</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Distance</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>High prices</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Limited offers</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>0.60970475101361887</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>0.1086651419066431</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>0.16823474373635514</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>0.11339536334338289</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-97FF-4E35-978F-856227513383}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1462893936"/>
+        <c:axId val="1462898736"/>
+      </c:barChart>
+      <c:valAx>
+        <c:axId val="1462898736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1462893936"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1462893936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1462898736"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
-        <a:sp3d/>
       </c:spPr>
-    </c:floor>
-    <c:sideWall>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:sideWall>
-    <c:backWall>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:backWall>
-    <c:plotArea>
-      <c:layout/>
-      <c:pie3DChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>challenges!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:explosion val="14"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d contourW="25400">
-                <a:contourClr>
-                  <a:schemeClr val="lt1"/>
-                </a:contourClr>
-              </a:sp3d>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-31CA-4F8D-8B62-7A3C86AEC9EB}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d contourW="25400">
-                <a:contourClr>
-                  <a:schemeClr val="lt1"/>
-                </a:contourClr>
-              </a:sp3d>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000004-31CA-4F8D-8B62-7A3C86AEC9EB}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d contourW="25400">
-                <a:contourClr>
-                  <a:schemeClr val="lt1"/>
-                </a:contourClr>
-              </a:sp3d>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000006-31CA-4F8D-8B62-7A3C86AEC9EB}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:sp3d contourW="25400">
-                <a:contourClr>
-                  <a:schemeClr val="lt1"/>
-                </a:contourClr>
-              </a:sp3d>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000008-31CA-4F8D-8B62-7A3C86AEC9EB}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="-60000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="75000"/>
-                          <a:lumOff val="25000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout>
-                    <c:manualLayout>
-                      <c:w val="0.17287689306216403"/>
-                      <c:h val="0.20534765122676077"/>
-                    </c:manualLayout>
-                  </c15:layout>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-31CA-4F8D-8B62-7A3C86AEC9EB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="35000"/>
-                      <a:lumOff val="65000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:round/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>challenges!$A$4:$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Crowding</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Distance</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>High prices</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Limited offers</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>challenges!$B$4:$B$8</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.60970475101361887</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.1086651419066431</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.16823474373635514</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.11339536334338289</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-31CA-4F8D-8B62-7A3C86AEC9EB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-      </c:pie3DChart>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
@@ -4266,6 +3969,7 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:userShapes r:id="rId3"/>
   <c:extLst/>
 </c:chartSpace>
 </file>
@@ -4390,6 +4094,12 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
+  <a:schemeClr val="accent5"/>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -5575,6 +5285,509 @@
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5971,15 +6184,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>132108</xdr:rowOff>
+      <xdr:rowOff>74958</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6009,13 +6222,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>590551</xdr:colOff>
+      <xdr:colOff>590552</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>561976</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
@@ -6046,23 +6259,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
+        <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E3F5C5A-57CF-4EFD-9072-31EC33B2E0FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BF9D6A5-B315-40D9-9F37-F93317BCCA06}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6082,7 +6295,450 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C00A5CC3-BFA2-76FF-EE84-3A33F98BC007}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9753600" y="123825"/>
+          <a:ext cx="4000500" cy="2324100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>insights</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>consumers start buying essentials</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> last week before ramadan.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>category which see the highest spend increase  is beverags.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3_discounts is the most</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> offers that </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>effective</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> on </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> purchase decisions.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4_the main challenges while shopping in ramadanis crowding .</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.18958</cdr:x>
+      <cdr:y>0.0855</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.94792</cdr:x>
+      <cdr:y>0.15985</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CF271AB-A1AB-D9C2-5424-3F41A34DEE9B}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="866775" y="219076"/>
+          <a:ext cx="3467100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t>When do consumers start buying essentials?</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.13996</cdr:x>
+      <cdr:y>0</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.91684</cdr:x>
+      <cdr:y>0.08016</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F4EC617-B89E-C55B-7646-97E3B319A642}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="657225" y="-28574"/>
+          <a:ext cx="3648075" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t>Which categories see the highest spend increase? </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.41444</cdr:x>
+      <cdr:y>0.37166</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.58556</cdr:x>
+      <cdr:y>0.62834</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FB6DB3A-FB3F-63ED-25C0-44D6E9D42582}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="2214562" y="1323974"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.13191</cdr:x>
+      <cdr:y>0.06417</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.94652</cdr:x>
+      <cdr:y>0.1738</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDDEF6E7-520B-4E20-5133-6A1A432DD69F}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="704850" y="228600"/>
+          <a:ext cx="4352925" cy="390525"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t>What are the main challenges while shopping in ramadan</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="challenges"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
